--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99250</v>
+        <v>99253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99253</v>
+        <v>99254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104786</v>
+        <v>7104787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544041</v>
       </c>
       <c r="B2" t="n">
-        <v>43316</v>
+        <v>43318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99254</v>
+        <v>99259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104786</v>
+        <v>7104787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Linn Andersson Linder</t>
+          <t>Linn Andersson Linder, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linn Andersson Linder, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Linn Andersson Linder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99267</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104786</v>
+        <v>7104787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99269</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104786</v>
+        <v>7104787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99282</v>
+        <v>99284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544041</v>
       </c>
       <c r="B2" t="n">
-        <v>43318</v>
+        <v>43331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99284</v>
+        <v>99297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37566-2024 artfynd.xlsx
+++ b/artfynd/A 37566-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544041</v>
       </c>
       <c r="B2" t="n">
-        <v>43331</v>
+        <v>43333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136547545</v>
       </c>
       <c r="B3" t="n">
-        <v>99297</v>
+        <v>99299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>561443</v>
       </c>
       <c r="R3" t="n">
-        <v>7104787</v>
+        <v>7104786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
